--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/13_evidence_sources.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/13_evidence_sources.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Raeafb00acfcb421b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R65272815c76942fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rd90c9a21e8864c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R6c92cff1f7e04201"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R6276bedb472e4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R5fdfdd33d6f4481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R5f60b20c2c654ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rb0866dcaf43443db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R78f1b061513f4174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R18372a8243cc4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Re7927e10649e4e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Re9c67f34ddcc4ea9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -622,7 +622,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R872d896912ca459b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa8492c7eff24061"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -773,7 +773,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-enterprise-ev01.json</x:v>
       </x:c>
       <x:c r="L6" s="78" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-ENTERPRISE-EV01 - AbarVa executive profile interview (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M6" s="41" t="str">
         <x:v>High</x:v>
@@ -814,7 +814,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-enterprise-ev02.json</x:v>
       </x:c>
       <x:c r="L7" s="79" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-ENTERPRISE-EV02 - FY26 enterprise strategy workshop (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M7" s="45" t="str">
         <x:v>High</x:v>
@@ -855,7 +855,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-clinical-ops-ev01.json</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01 - Epic application inventory (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M8" t="str">
         <x:v>High</x:v>
@@ -896,7 +896,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-clinical-ops-ev02.json</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV02 - Clinical operations workshop notes (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M9" t="str">
         <x:v>High</x:v>
@@ -937,7 +937,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-claims-ops-ev01.json</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01 - Claims platform extract (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M10" t="str">
         <x:v>High</x:v>
@@ -978,7 +978,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-claims-ops-ev02.json</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV02 - Claims analytics SME interview (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>High</x:v>
@@ -1019,7 +1019,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-eligibility-ev01.json</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01 - Eligibility file inventory (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M12" t="str">
         <x:v>High</x:v>
@@ -1060,7 +1060,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-eligibility-ev02.json</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-ELIGIBILITY-EV02 - Benefits configuration extract (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>High</x:v>
@@ -1101,7 +1101,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-prior-auth-ev01.json</x:v>
       </x:c>
       <x:c r="L14" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01 - Prior auth workflow export (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M14" t="str">
         <x:v>High</x:v>
@@ -1142,7 +1142,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-prior-auth-ev02.json</x:v>
       </x:c>
       <x:c r="L15" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV02 - UM clinical review sample (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M15" t="str">
         <x:v>High</x:v>
@@ -1183,7 +1183,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-contact-center-ev01.json</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01 - Call transcript sample pack (record 11) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M16" t="str">
         <x:v>High</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-contact-center-ev02.json</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV02 - CRM case extract (record 12) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M17" t="str">
         <x:v>High</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-revenue-cycle-ev01.json</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01 - RCM process map (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M18" t="str">
         <x:v>High</x:v>
@@ -1306,7 +1306,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-revenue-cycle-ev02.json</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV02 - Denials dashboard inventory (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M19" t="str">
         <x:v>High</x:v>
@@ -1347,7 +1347,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-finance-analytics-ev01.json</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01 - Oracle ERP finance extract (record 15) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M20" t="str">
         <x:v>High</x:v>
@@ -1388,7 +1388,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-finance-analytics-ev02.json</x:v>
       </x:c>
       <x:c r="L21" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV02 - Finance mart lineage workshop (record 16) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M21" t="str">
         <x:v>High</x:v>
@@ -1429,7 +1429,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-hr-workforce-ev01.json</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01 - Workday HCM extract (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M22" t="str">
         <x:v>High</x:v>
@@ -1470,7 +1470,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-hr-workforce-ev02.json</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV02 - Workforce planning workbook (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>High</x:v>
@@ -1511,7 +1511,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-clinical-quality-ev01.json</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01 - Quality measure inventory (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M24" t="str">
         <x:v>High</x:v>
@@ -1552,7 +1552,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-clinical-quality-ev02.json</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV02 - HEDIS/STAR reporting workbook (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M25" t="str">
         <x:v>High</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-claims-analytics-ev01.json</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01 - Claims mart inventory (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M26" t="str">
         <x:v>High</x:v>
@@ -1634,7 +1634,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-claims-analytics-ev02.json</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV02 - Payment integrity analytic sample (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>High</x:v>
@@ -1675,7 +1675,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-provider-performance-ev01.json</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01 - Provider attribution extract (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>High</x:v>
@@ -1716,7 +1716,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-provider-performance-ev02.json</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV02 - Network contract scorecard (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>High</x:v>
@@ -1757,7 +1757,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-data-platform-ev01.json</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01 - Data platform architecture draft (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M30" t="str">
         <x:v>High</x:v>
@@ -1798,7 +1798,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-data-platform-ev02.json</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV02 - AWS/Databricks landing zone checklist (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M31" t="str">
         <x:v>High</x:v>
@@ -1839,7 +1839,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-data-governance-ev01.json</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01 - Data governance charter (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M32" t="str">
         <x:v>High</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-data-governance-ev02.json</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV02 - Collibra catalog export (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M33" t="str">
         <x:v>High</x:v>
@@ -1921,7 +1921,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-agent-assist-ev01.json</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01 - Agent assist discovery workshop (record 29) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>High</x:v>
@@ -1962,7 +1962,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-agent-assist-ev02.json</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV02 - Transcript annotation sample (record 30) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>High</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-unified-lakehouse-ev01.json</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01 - Clinical claims lakehouse blueprint (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>High</x:v>
@@ -2044,7 +2044,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-unified-lakehouse-ev02.json</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV02 - Epic/claims/pharmacy source inventory (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M37" t="str">
         <x:v>High</x:v>
@@ -2085,7 +2085,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-it-budget-ev01.json</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-IT-BUDGET-EV01 - FY26 IT budget export (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M38" t="str">
         <x:v>High</x:v>
@@ -2126,7 +2126,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-it-budget-ev02.json</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-IT-BUDGET-EV02 - Tower baseline workshop (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M39" t="str">
         <x:v>High</x:v>
@@ -2167,7 +2167,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-vendor-sourcing-ev01.json</x:v>
       </x:c>
       <x:c r="L40" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01 - Vendor contract extract (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M40" t="str">
         <x:v>High</x:v>
@@ -2208,7 +2208,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-vendor-sourcing-ev02.json</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV02 - AP spend export (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M41" t="str">
         <x:v>High</x:v>
@@ -2249,7 +2249,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-cmdb-infra-ev01.json</x:v>
       </x:c>
       <x:c r="L42" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01 - ServiceNow CMDB export (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M42" t="str">
         <x:v>High</x:v>
@@ -2290,7 +2290,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-cmdb-infra-ev02.json</x:v>
       </x:c>
       <x:c r="L43" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for MERIDIAN-HEALTH-MH-CMDB-INFRA-EV02 - Cloud inventory extract (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M43" t="str">
         <x:v>High</x:v>
@@ -2331,7 +2331,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-incidents-ev01.json</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile MERIDIAN-HEALTH-MH-INCIDENTS-EV01 - ServiceNow incident export (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M44" t="str">
         <x:v>High</x:v>
@@ -2372,7 +2372,7 @@
         <x:v>tenant-inputs/generated/meridian-health/standard-2026-07-v3/evidence-manifest/meridian-health-mh-incidents-ev02.json</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for MERIDIAN-HEALTH-MH-INCIDENTS-EV02 - Change advisory board log (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M45" t="str">
         <x:v>High</x:v>
@@ -2402,7 +2402,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3b3ae4d83324733"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf40ddde59fd34adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2477,7 +2477,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08e96b934eeb4fc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf22dd9d0e1f14134"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2641,7 +2641,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1e7ff659f304994"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2b551bfb774ab1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2727,7 +2727,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra023938f5f26441b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b477119fbd64eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2837,7 +2837,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R035e9a21e4a44b85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R003b39ec423e45d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>